--- a/sorties/resultats.xlsx
+++ b/sorties/resultats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://istainternational-my.sharepoint.com/personal/remi_fondin_ista_com/Documents/Perso/memoire-data-culture/memoire-poc/sorties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_DF706F5E49B78A457F00592D6C08451723565C9B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A62104AA-A446-445F-AD2F-7FB5B6A8E747}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_D7DC8F4949A706495F415756546E4CD7021E688A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2ABDCC2-E0CB-47FA-8344-B67BD07EAF74}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mouvements" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="376">
   <si>
     <t>titre</t>
   </si>
@@ -45,7 +45,13 @@
     <t>convention_distance</t>
   </si>
   <si>
-    <t>masse_kg_imputee</t>
+    <t>nb_oeuvres</t>
+  </si>
+  <si>
+    <t>masse_kg_unitaire</t>
+  </si>
+  <si>
+    <t>masse_kg_totale</t>
   </si>
   <si>
     <t>mode</t>
@@ -958,10 +964,19 @@
     <t>Non utilisée pour la distance</t>
   </si>
   <si>
+    <t>Nombre d'œuvres du lot</t>
+  </si>
+  <si>
+    <t>Disponible (dos_nb_oeu_coll/hcoll)</t>
+  </si>
+  <si>
+    <t>Masse sommée sur toutes les œuvres du mouvement</t>
+  </si>
+  <si>
     <t>Masse de l'œuvre</t>
   </si>
   <si>
-    <t>Forfait par domaine (hypothèse assumée)</t>
+    <t>Forfait par domaine dominant, appliqué à chaque œuvre du lot (hypothèse assumée)</t>
   </si>
   <si>
     <t>Masse du conditionnement</t>
@@ -1085,6 +1100,15 @@
   </si>
   <si>
     <t>Hypothèse de travail assumée</t>
+  </si>
+  <si>
+    <t>Masse du mouvement</t>
+  </si>
+  <si>
+    <t>masse unitaire × nombre d'œuvres du lot</t>
+  </si>
+  <si>
+    <t>Navigart : dos_nb_oeu_coll + dos_nb_oeu_hcoll (domaine dominant supposé pour tout le lot)</t>
   </si>
   <si>
     <t>Conditionnement</t>
@@ -1469,15 +1493,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="61.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1511,3483 +1533,4089 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>4.4000000000000004</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
         <v>26</v>
       </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
       <c r="J2">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K2">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>374.4</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3">
-        <v>5.2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>5.2</v>
       </c>
       <c r="J3">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K3">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15.6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M3">
+        <v>0.51100000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4">
         <v>16476.8</v>
       </c>
       <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>26</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>26</v>
       </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4">
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4">
         <v>1.01</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>432.68099999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>333.1</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H5">
-        <v>5.2</v>
-      </c>
-      <c r="I5" t="s">
-        <v>17</v>
+        <v>44</v>
+      </c>
+      <c r="I5">
+        <v>5.2</v>
       </c>
       <c r="J5">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K5">
-        <v>0.152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>228.8</v>
+      </c>
+      <c r="K5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M5">
+        <v>6.6689999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>237.3</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H6">
-        <v>5.2</v>
-      </c>
-      <c r="I6" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>5.2</v>
       </c>
       <c r="J6">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K6">
-        <v>0.108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.6</v>
+      </c>
+      <c r="K6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M6">
+        <v>1.9430000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>175.3</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H7">
-        <v>5.2</v>
-      </c>
-      <c r="I7" t="s">
-        <v>17</v>
+        <v>155</v>
+      </c>
+      <c r="I7">
+        <v>5.2</v>
       </c>
       <c r="J7">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>806</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M7">
+        <v>12.363</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8">
         <v>303.5</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H8">
-        <v>5.2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <v>5.2</v>
       </c>
       <c r="J8">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K8">
-        <v>0.13800000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M8">
+        <v>2.4860000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>5.2</v>
-      </c>
-      <c r="I9" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>5.2</v>
       </c>
       <c r="J9">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K9">
+        <v>5.2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F10">
         <v>119.1</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H10">
-        <v>5.2</v>
-      </c>
-      <c r="I10" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>5.2</v>
       </c>
       <c r="J10">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K10">
-        <v>5.3999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>20.8</v>
+      </c>
+      <c r="K10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M10">
+        <v>0.217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11">
         <v>1126.2</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H11">
-        <v>5.2</v>
-      </c>
-      <c r="I11" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>5.2</v>
       </c>
       <c r="J11">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K11">
+        <v>5.2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M11">
         <v>0.51200000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12">
         <v>1535.8</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>78</v>
       </c>
-      <c r="I12" t="s">
-        <v>17</v>
-      </c>
       <c r="J12">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K12">
+        <v>78</v>
+      </c>
+      <c r="K12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M12">
         <v>10.481999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13">
         <v>19145.400000000001</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H13">
-        <v>5.2</v>
-      </c>
-      <c r="I13" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>5.2</v>
       </c>
       <c r="J13">
+        <v>15.6</v>
+      </c>
+      <c r="K13" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13">
         <v>1.01</v>
       </c>
-      <c r="K13">
-        <v>100.55200000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M13">
+        <v>301.65499999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>5.2</v>
-      </c>
-      <c r="I14" t="s">
-        <v>17</v>
+        <v>142</v>
+      </c>
+      <c r="I14">
+        <v>5.2</v>
       </c>
       <c r="J14">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K14">
+        <v>738.4</v>
+      </c>
+      <c r="K14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15">
         <v>225.4</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H15">
-        <v>5.2</v>
-      </c>
-      <c r="I15" t="s">
-        <v>17</v>
+        <v>26</v>
+      </c>
+      <c r="I15">
+        <v>5.2</v>
       </c>
       <c r="J15">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K15">
-        <v>0.10299999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="K15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M15">
+        <v>2.6659999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F16">
         <v>231.6</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H16">
-        <v>5.2</v>
-      </c>
-      <c r="I16" t="s">
-        <v>17</v>
+        <v>34</v>
+      </c>
+      <c r="I16">
+        <v>5.2</v>
       </c>
       <c r="J16">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K16">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>176.8</v>
+      </c>
+      <c r="K16" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M16">
+        <v>3.5830000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F17">
         <v>399.4</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H17">
-        <v>5.2</v>
-      </c>
-      <c r="I17" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="I17">
+        <v>5.2</v>
       </c>
       <c r="J17">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K17">
-        <v>0.182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>57.2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M17">
+        <v>1.9990000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F18">
         <v>390.3</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H18">
-        <v>5.2</v>
-      </c>
-      <c r="I18" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>5.2</v>
       </c>
       <c r="J18">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K18">
-        <v>0.17799999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10.4</v>
+      </c>
+      <c r="K18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M18">
+        <v>0.35499999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F19">
         <v>2461.1</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H19">
-        <v>5.2</v>
-      </c>
-      <c r="I19" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>5.2</v>
       </c>
       <c r="J19">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K19">
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10.4</v>
+      </c>
+      <c r="K19" t="s">
+        <v>19</v>
+      </c>
+      <c r="L19">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M19">
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>5.2</v>
-      </c>
-      <c r="I20" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="I20">
+        <v>5.2</v>
       </c>
       <c r="J20">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K20">
+        <v>275.60000000000002</v>
+      </c>
+      <c r="K20" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21">
         <v>2305</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H21">
-        <v>5.2</v>
-      </c>
-      <c r="I21" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>5.2</v>
       </c>
       <c r="J21">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K21">
-        <v>1.0489999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>20.8</v>
+      </c>
+      <c r="K21" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M21">
+        <v>4.1950000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F22">
         <v>225.4</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H22">
-        <v>5.2</v>
-      </c>
-      <c r="I22" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="I22">
+        <v>5.2</v>
       </c>
       <c r="J22">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K22">
-        <v>0.10299999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="K22" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M22">
+        <v>0.51300000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
         <v>35</v>
       </c>
-      <c r="B23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F23">
         <v>237.3</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H23">
-        <v>5.2</v>
-      </c>
-      <c r="I23" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="I23">
+        <v>5.2</v>
       </c>
       <c r="J23">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K23">
-        <v>0.108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="K23" t="s">
+        <v>19</v>
+      </c>
+      <c r="L23">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M23">
+        <v>2.1589999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F24">
         <v>202</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H24">
-        <v>5.2</v>
-      </c>
-      <c r="I24" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="I24">
+        <v>5.2</v>
       </c>
       <c r="J24">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K24">
-        <v>9.1999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="K24" t="s">
+        <v>19</v>
+      </c>
+      <c r="L24">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M24">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25">
         <v>19488.400000000001</v>
       </c>
       <c r="G25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
         <v>26</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>26</v>
       </c>
-      <c r="I25" t="s">
-        <v>27</v>
-      </c>
-      <c r="J25">
+      <c r="K25" t="s">
+        <v>29</v>
+      </c>
+      <c r="L25">
         <v>1.01</v>
       </c>
-      <c r="K25">
+      <c r="M25">
         <v>511.76499999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F26">
         <v>175.3</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H26">
-        <v>5.2</v>
-      </c>
-      <c r="I26" t="s">
-        <v>17</v>
+        <v>81</v>
+      </c>
+      <c r="I26">
+        <v>5.2</v>
       </c>
       <c r="J26">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K26">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>421.2</v>
+      </c>
+      <c r="K26" t="s">
+        <v>19</v>
+      </c>
+      <c r="L26">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M26">
+        <v>6.4610000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>185.3</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H27">
-        <v>5.2</v>
-      </c>
-      <c r="I27" t="s">
-        <v>17</v>
+        <v>38</v>
+      </c>
+      <c r="I27">
+        <v>5.2</v>
       </c>
       <c r="J27">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K27">
-        <v>8.4000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>197.6</v>
+      </c>
+      <c r="K27" t="s">
+        <v>19</v>
+      </c>
+      <c r="L27">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M27">
+        <v>3.2040000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F28">
         <v>376.4</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H28">
-        <v>5.2</v>
-      </c>
-      <c r="I28" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>5.2</v>
       </c>
       <c r="J28">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K28">
+        <v>5.2</v>
+      </c>
+      <c r="K28" t="s">
+        <v>19</v>
+      </c>
+      <c r="L28">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M28">
         <v>0.17100000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>5.2</v>
-      </c>
-      <c r="I29" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="I29">
+        <v>5.2</v>
       </c>
       <c r="J29">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K29">
+        <v>62.4</v>
+      </c>
+      <c r="K29" t="s">
+        <v>19</v>
+      </c>
+      <c r="L29">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F30">
         <v>17917</v>
       </c>
       <c r="G30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H30">
-        <v>5.2</v>
-      </c>
-      <c r="I30" t="s">
-        <v>27</v>
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>5.2</v>
       </c>
       <c r="J30">
+        <v>10.4</v>
+      </c>
+      <c r="K30" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30">
         <v>1.01</v>
       </c>
-      <c r="K30">
-        <v>94.1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M30">
+        <v>188.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F31">
         <v>326.2</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H31">
-        <v>5.2</v>
-      </c>
-      <c r="I31" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="I31">
+        <v>5.2</v>
       </c>
       <c r="J31">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K31">
-        <v>0.14799999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>46.8</v>
+      </c>
+      <c r="K31" t="s">
+        <v>19</v>
+      </c>
+      <c r="L31">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M31">
+        <v>1.3360000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F32">
         <v>99.8</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H32">
-        <v>5.2</v>
-      </c>
-      <c r="I32" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="I32">
+        <v>5.2</v>
       </c>
       <c r="J32">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K32">
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>83.2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>19</v>
+      </c>
+      <c r="L32">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M32">
+        <v>0.72699999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F33">
         <v>13606.4</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H33">
-        <v>5.2</v>
-      </c>
-      <c r="I33" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>5.2</v>
       </c>
       <c r="J33">
+        <v>5.2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>29</v>
+      </c>
+      <c r="L33">
         <v>1.01</v>
       </c>
-      <c r="K33">
+      <c r="M33">
         <v>71.460999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F34">
         <v>1641.6</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
         <v>26</v>
       </c>
-      <c r="I34" t="s">
-        <v>17</v>
-      </c>
       <c r="J34">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K34">
+        <v>26</v>
+      </c>
+      <c r="K34" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M34">
         <v>3.7349999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F35">
         <v>375.1</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H35">
-        <v>5.2</v>
-      </c>
-      <c r="I35" t="s">
-        <v>17</v>
+        <v>37</v>
+      </c>
+      <c r="I35">
+        <v>5.2</v>
       </c>
       <c r="J35">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K35">
-        <v>0.17100000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>192.4</v>
+      </c>
+      <c r="K35" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M35">
+        <v>6.3150000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F36">
         <v>1918.1</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H36">
-        <v>5.2</v>
-      </c>
-      <c r="I36" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>5.2</v>
       </c>
       <c r="J36">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K36">
+        <v>5.2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>19</v>
+      </c>
+      <c r="L36">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M36">
         <v>0.873</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F37">
         <v>237.3</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H37">
-        <v>5.2</v>
-      </c>
-      <c r="I37" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>5.2</v>
       </c>
       <c r="J37">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K37">
+        <v>5.2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>19</v>
+      </c>
+      <c r="L37">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M37">
         <v>0.108</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F38">
         <v>2186</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
         <v>19.5</v>
       </c>
-      <c r="I38" t="s">
-        <v>17</v>
-      </c>
       <c r="J38">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K38">
+        <v>19.5</v>
+      </c>
+      <c r="K38" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M38">
         <v>3.73</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F39">
         <v>202</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H39">
-        <v>5.2</v>
-      </c>
-      <c r="I39" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="I39">
+        <v>5.2</v>
       </c>
       <c r="J39">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K39">
-        <v>9.1999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>275.60000000000002</v>
+      </c>
+      <c r="K39" t="s">
+        <v>19</v>
+      </c>
+      <c r="L39">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M39">
+        <v>4.8710000000000004</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B40" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F40">
         <v>19704.900000000001</v>
       </c>
       <c r="G40" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H40">
-        <v>5.2</v>
-      </c>
-      <c r="I40" t="s">
-        <v>27</v>
+        <v>286</v>
+      </c>
+      <c r="I40">
+        <v>5.2</v>
       </c>
       <c r="J40">
+        <v>1487.2</v>
+      </c>
+      <c r="K40" t="s">
+        <v>29</v>
+      </c>
+      <c r="L40">
         <v>1.01</v>
       </c>
-      <c r="K40">
-        <v>103.49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M40">
+        <v>29598.179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F41">
         <v>139.1</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H41">
-        <v>5.2</v>
-      </c>
-      <c r="I41" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="I41">
+        <v>5.2</v>
       </c>
       <c r="J41">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K41">
-        <v>6.3E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.6</v>
+      </c>
+      <c r="K41" t="s">
+        <v>19</v>
+      </c>
+      <c r="L41">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M41">
+        <v>1.139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F42">
         <v>187.3</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H42">
-        <v>5.2</v>
-      </c>
-      <c r="I42" t="s">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="I42">
+        <v>5.2</v>
       </c>
       <c r="J42">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K42">
-        <v>8.5000000000000006E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>213.2</v>
+      </c>
+      <c r="K42" t="s">
+        <v>19</v>
+      </c>
+      <c r="L42">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M42">
+        <v>3.4940000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C43" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E43" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F43">
         <v>202</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H43">
-        <v>5.2</v>
-      </c>
-      <c r="I43" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="I43">
+        <v>5.2</v>
       </c>
       <c r="J43">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K43">
-        <v>9.1999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10.4</v>
+      </c>
+      <c r="K43" t="s">
+        <v>19</v>
+      </c>
+      <c r="L43">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M43">
+        <v>0.184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F44">
         <v>375.1</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
         <v>19.5</v>
       </c>
-      <c r="I44" t="s">
-        <v>17</v>
-      </c>
       <c r="J44">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K44">
+        <v>19.5</v>
+      </c>
+      <c r="K44" t="s">
+        <v>19</v>
+      </c>
+      <c r="L44">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M44">
         <v>0.64</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F45">
         <v>378.8</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H45">
-        <v>5.2</v>
-      </c>
-      <c r="I45" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="I45">
+        <v>5.2</v>
       </c>
       <c r="J45">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K45">
-        <v>0.17199999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="K45" t="s">
+        <v>19</v>
+      </c>
+      <c r="L45">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M45">
+        <v>0.86199999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F46">
         <v>4.4000000000000004</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H46">
-        <v>5.2</v>
-      </c>
-      <c r="I46" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="I46">
+        <v>5.2</v>
       </c>
       <c r="J46">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K46">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="K46" t="s">
+        <v>19</v>
+      </c>
+      <c r="L46">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M46">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F47">
         <v>377.9</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H47">
-        <v>5.2</v>
-      </c>
-      <c r="I47" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>5.2</v>
       </c>
       <c r="J47">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K47">
+        <v>5.2</v>
+      </c>
+      <c r="K47" t="s">
+        <v>19</v>
+      </c>
+      <c r="L47">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M47">
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B48" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D48" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E48" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F48">
         <v>523.70000000000005</v>
       </c>
       <c r="G48" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H48">
-        <v>5.2</v>
-      </c>
-      <c r="I48" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="I48">
+        <v>5.2</v>
       </c>
       <c r="J48">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K48">
-        <v>0.23799999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>46.8</v>
+      </c>
+      <c r="K48" t="s">
+        <v>19</v>
+      </c>
+      <c r="L48">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M48">
+        <v>2.145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C49" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F49">
         <v>197.9</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H49">
-        <v>5.2</v>
-      </c>
-      <c r="I49" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="I49">
+        <v>5.2</v>
       </c>
       <c r="J49">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K49">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <v>124.8</v>
+      </c>
+      <c r="K49" t="s">
+        <v>19</v>
+      </c>
+      <c r="L49">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M49">
+        <v>2.161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F50">
         <v>376.4</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H50">
-        <v>5.2</v>
-      </c>
-      <c r="I50" t="s">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="I50">
+        <v>5.2</v>
       </c>
       <c r="J50">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K50">
-        <v>0.17100000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15.6</v>
+      </c>
+      <c r="K50" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M50">
+        <v>0.51400000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F51">
         <v>376.4</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H51">
-        <v>5.2</v>
-      </c>
-      <c r="I51" t="s">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="I51">
+        <v>5.2</v>
       </c>
       <c r="J51">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K51">
-        <v>0.17100000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15.6</v>
+      </c>
+      <c r="K51" t="s">
+        <v>19</v>
+      </c>
+      <c r="L51">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M51">
+        <v>0.51400000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E52" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F52">
         <v>404.7</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H52">
-        <v>5.2</v>
-      </c>
-      <c r="I52" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="I52">
+        <v>5.2</v>
       </c>
       <c r="J52">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K52">
-        <v>0.184</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+        <v>119.6</v>
+      </c>
+      <c r="K52" t="s">
+        <v>19</v>
+      </c>
+      <c r="L52">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M52">
+        <v>4.2350000000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F53">
         <v>721.1</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
         <v>78</v>
       </c>
-      <c r="I53" t="s">
-        <v>17</v>
-      </c>
       <c r="J53">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K53">
+        <v>78</v>
+      </c>
+      <c r="K53" t="s">
+        <v>19</v>
+      </c>
+      <c r="L53">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M53">
         <v>4.9219999999999997</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C54" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E54" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F54">
         <v>418.4</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H54">
-        <v>5.2</v>
-      </c>
-      <c r="I54" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="I54">
+        <v>5.2</v>
       </c>
       <c r="J54">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K54">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+        <v>171.6</v>
+      </c>
+      <c r="K54" t="s">
+        <v>19</v>
+      </c>
+      <c r="L54">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M54">
+        <v>6.282</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C55" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E55" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F55">
         <v>2557.4</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H55">
-        <v>5.2</v>
-      </c>
-      <c r="I55" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="I55">
+        <v>5.2</v>
       </c>
       <c r="J55">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K55">
-        <v>1.1639999999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+        <v>41.6</v>
+      </c>
+      <c r="K55" t="s">
+        <v>19</v>
+      </c>
+      <c r="L55">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M55">
+        <v>9.3089999999999993</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F56">
         <v>261.3</v>
       </c>
       <c r="G56" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H56">
-        <v>5.2</v>
-      </c>
-      <c r="I56" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="I56">
+        <v>5.2</v>
       </c>
       <c r="J56">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K56">
-        <v>0.11899999999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="K56" t="s">
+        <v>19</v>
+      </c>
+      <c r="L56">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M56">
+        <v>0.59399999999999997</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C57" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E57" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F57">
         <v>406</v>
       </c>
       <c r="G57" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
         <v>78</v>
       </c>
-      <c r="I57" t="s">
-        <v>17</v>
-      </c>
       <c r="J57">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K57">
+        <v>78</v>
+      </c>
+      <c r="K57" t="s">
+        <v>19</v>
+      </c>
+      <c r="L57">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M57">
         <v>2.7709999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C58" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E58" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F58">
         <v>305</v>
       </c>
       <c r="G58" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H58">
-        <v>5.2</v>
-      </c>
-      <c r="I58" t="s">
-        <v>17</v>
+        <v>84</v>
+      </c>
+      <c r="I58">
+        <v>5.2</v>
       </c>
       <c r="J58">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K58">
-        <v>0.13900000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+        <v>436.8</v>
+      </c>
+      <c r="K58" t="s">
+        <v>19</v>
+      </c>
+      <c r="L58">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M58">
+        <v>11.657</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C59" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E59" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F59">
         <v>173.4</v>
       </c>
       <c r="G59" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H59">
-        <v>5.2</v>
-      </c>
-      <c r="I59" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>5.2</v>
       </c>
       <c r="J59">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K59">
-        <v>7.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+        <v>20.8</v>
+      </c>
+      <c r="K59" t="s">
+        <v>19</v>
+      </c>
+      <c r="L59">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M59">
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E60" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>5.2</v>
-      </c>
-      <c r="I60" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I60">
+        <v>5.2</v>
       </c>
       <c r="J60">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K60">
+        <v>5.2</v>
+      </c>
+      <c r="K60" t="s">
+        <v>19</v>
+      </c>
+      <c r="L60">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E61" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F61">
         <v>1676.6</v>
       </c>
       <c r="G61" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
         <v>26</v>
       </c>
-      <c r="I61" t="s">
-        <v>17</v>
-      </c>
       <c r="J61">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K61">
+        <v>26</v>
+      </c>
+      <c r="K61" t="s">
+        <v>19</v>
+      </c>
+      <c r="L61">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M61">
         <v>3.8140000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E62" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="H62">
-        <v>5.2</v>
-      </c>
-      <c r="I62" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="I62">
+        <v>5.2</v>
       </c>
       <c r="J62">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K62">
+        <v>124.8</v>
+      </c>
+      <c r="K62" t="s">
+        <v>19</v>
+      </c>
+      <c r="L62">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M62">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E63" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F63">
         <v>139.1</v>
       </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H63">
-        <v>5.2</v>
-      </c>
-      <c r="I63" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="I63">
+        <v>5.2</v>
       </c>
       <c r="J63">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K63">
-        <v>6.3E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+        <v>20.8</v>
+      </c>
+      <c r="K63" t="s">
+        <v>19</v>
+      </c>
+      <c r="L63">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M63">
+        <v>0.253</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F64">
         <v>302.7</v>
       </c>
       <c r="G64" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H64">
-        <v>5.2</v>
-      </c>
-      <c r="I64" t="s">
-        <v>17</v>
+        <v>7</v>
+      </c>
+      <c r="I64">
+        <v>5.2</v>
       </c>
       <c r="J64">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K64">
-        <v>0.13800000000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+        <v>36.4</v>
+      </c>
+      <c r="K64" t="s">
+        <v>19</v>
+      </c>
+      <c r="L64">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M64">
+        <v>0.96399999999999997</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C65" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F65">
         <v>261.3</v>
       </c>
       <c r="G65" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H65">
-        <v>5.2</v>
-      </c>
-      <c r="I65" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="I65">
+        <v>5.2</v>
       </c>
       <c r="J65">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K65">
-        <v>0.11899999999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+        <v>93.6</v>
+      </c>
+      <c r="K65" t="s">
+        <v>19</v>
+      </c>
+      <c r="L65">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M65">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D66" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E66" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F66">
         <v>404.4</v>
       </c>
       <c r="G66" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H66">
-        <v>5.2</v>
-      </c>
-      <c r="I66" t="s">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="I66">
+        <v>5.2</v>
       </c>
       <c r="J66">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K66">
-        <v>0.184</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15.6</v>
+      </c>
+      <c r="K66" t="s">
+        <v>19</v>
+      </c>
+      <c r="L66">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M66">
+        <v>0.55200000000000005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C67" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F67">
         <v>402.7</v>
       </c>
       <c r="G67" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H67">
-        <v>5.2</v>
-      </c>
-      <c r="I67" t="s">
-        <v>17</v>
+        <v>50</v>
+      </c>
+      <c r="I67">
+        <v>5.2</v>
       </c>
       <c r="J67">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K67">
-        <v>0.183</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+      <c r="K67" t="s">
+        <v>19</v>
+      </c>
+      <c r="L67">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M67">
+        <v>9.1609999999999996</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B68" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C68" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D68" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F68">
         <v>305</v>
       </c>
       <c r="G68" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H68">
-        <v>5.2</v>
-      </c>
-      <c r="I68" t="s">
         <v>17</v>
       </c>
+      <c r="I68">
+        <v>5.2</v>
+      </c>
       <c r="J68">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K68">
-        <v>0.13900000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+        <v>88.4</v>
+      </c>
+      <c r="K68" t="s">
+        <v>19</v>
+      </c>
+      <c r="L68">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M68">
+        <v>2.359</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B69" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C69" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E69" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F69">
         <v>233.1</v>
       </c>
       <c r="G69" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H69">
-        <v>5.2</v>
-      </c>
-      <c r="I69" t="s">
-        <v>17</v>
+        <v>29</v>
+      </c>
+      <c r="I69">
+        <v>5.2</v>
       </c>
       <c r="J69">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K69">
-        <v>0.106</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="K69" t="s">
+        <v>19</v>
+      </c>
+      <c r="L69">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M69">
+        <v>3.0760000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C70" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E70" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F70">
         <v>2535.9</v>
       </c>
       <c r="G70" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H70">
-        <v>5.2</v>
-      </c>
-      <c r="I70" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>5.2</v>
       </c>
       <c r="J70">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K70">
+        <v>5.2</v>
+      </c>
+      <c r="K70" t="s">
+        <v>19</v>
+      </c>
+      <c r="L70">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M70">
         <v>1.1539999999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B71" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C71" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F71">
         <v>187.3</v>
       </c>
       <c r="G71" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H71">
-        <v>5.2</v>
-      </c>
-      <c r="I71" t="s">
-        <v>17</v>
+        <v>46</v>
+      </c>
+      <c r="I71">
+        <v>5.2</v>
       </c>
       <c r="J71">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K71">
-        <v>8.5000000000000006E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+        <v>239.2</v>
+      </c>
+      <c r="K71" t="s">
+        <v>19</v>
+      </c>
+      <c r="L71">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M71">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B72" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E72" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F72">
         <v>326.2</v>
       </c>
       <c r="G72" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H72">
-        <v>5.2</v>
-      </c>
-      <c r="I72" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="I72">
+        <v>5.2</v>
       </c>
       <c r="J72">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K72">
-        <v>0.14799999999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+        <v>57.2</v>
+      </c>
+      <c r="K72" t="s">
+        <v>19</v>
+      </c>
+      <c r="L72">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M72">
+        <v>1.633</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B73" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C73" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E73" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F73">
         <v>231.6</v>
       </c>
       <c r="G73" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H73">
-        <v>5.2</v>
-      </c>
-      <c r="I73" t="s">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="I73">
+        <v>5.2</v>
       </c>
       <c r="J73">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K73">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+        <v>249.6</v>
+      </c>
+      <c r="K73" t="s">
+        <v>19</v>
+      </c>
+      <c r="L73">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M73">
+        <v>5.0579999999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B74" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C74" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D74" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E74" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F74">
         <v>175.3</v>
       </c>
       <c r="G74" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H74">
-        <v>5.2</v>
-      </c>
-      <c r="I74" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>5.2</v>
       </c>
       <c r="J74">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K74">
+        <v>5.2</v>
+      </c>
+      <c r="K74" t="s">
+        <v>19</v>
+      </c>
+      <c r="L74">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M74">
         <v>0.08</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B75" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C75" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E75" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F75">
         <v>9.3000000000000007</v>
       </c>
       <c r="G75" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H75">
-        <v>5.2</v>
-      </c>
-      <c r="I75" t="s">
-        <v>17</v>
+        <v>33</v>
+      </c>
+      <c r="I75">
+        <v>5.2</v>
       </c>
       <c r="J75">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K75">
-        <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+        <v>171.6</v>
+      </c>
+      <c r="K75" t="s">
+        <v>19</v>
+      </c>
+      <c r="L75">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M75">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C76" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E76" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F76">
         <v>119.1</v>
       </c>
       <c r="G76" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H76">
-        <v>5.2</v>
-      </c>
-      <c r="I76" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I76">
+        <v>5.2</v>
       </c>
       <c r="J76">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K76">
+        <v>5.2</v>
+      </c>
+      <c r="K76" t="s">
+        <v>19</v>
+      </c>
+      <c r="L76">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M76">
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B77" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C77" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D77" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E77" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F77">
         <v>417</v>
       </c>
       <c r="G77" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H77">
-        <v>5.2</v>
-      </c>
-      <c r="I77" t="s">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="I77">
+        <v>5.2</v>
       </c>
       <c r="J77">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K77">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+        <v>140.4</v>
+      </c>
+      <c r="K77" t="s">
+        <v>19</v>
+      </c>
+      <c r="L77">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M77">
+        <v>5.1230000000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B78" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E78" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F78">
         <v>5.6</v>
       </c>
       <c r="G78" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H78">
+        <v>4</v>
+      </c>
+      <c r="I78">
         <v>19.5</v>
       </c>
-      <c r="I78" t="s">
-        <v>17</v>
-      </c>
       <c r="J78">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K78">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="K78" t="s">
+        <v>19</v>
+      </c>
+      <c r="L78">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M78">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B79" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E79" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F79">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>5.2</v>
-      </c>
-      <c r="I79" t="s">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="I79">
+        <v>5.2</v>
       </c>
       <c r="J79">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K79">
+        <v>57.2</v>
+      </c>
+      <c r="K79" t="s">
+        <v>19</v>
+      </c>
+      <c r="L79">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M79">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C80" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D80" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E80" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F80">
         <v>338.8</v>
       </c>
       <c r="G80" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H80">
-        <v>5.2</v>
-      </c>
-      <c r="I80" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I80">
+        <v>5.2</v>
       </c>
       <c r="J80">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K80">
+        <v>5.2</v>
+      </c>
+      <c r="K80" t="s">
+        <v>19</v>
+      </c>
+      <c r="L80">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M80">
         <v>0.154</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B81" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C81" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E81" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F81">
         <v>302.7</v>
       </c>
       <c r="G81" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H81">
-        <v>5.2</v>
-      </c>
-      <c r="I81" t="s">
-        <v>17</v>
+        <v>7</v>
+      </c>
+      <c r="I81">
+        <v>5.2</v>
       </c>
       <c r="J81">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K81">
-        <v>0.13800000000000001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+        <v>36.4</v>
+      </c>
+      <c r="K81" t="s">
+        <v>19</v>
+      </c>
+      <c r="L81">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M81">
+        <v>0.96399999999999997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B82" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D82" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E82" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F82">
         <v>1643.1</v>
       </c>
       <c r="G82" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H82">
-        <v>5.2</v>
-      </c>
-      <c r="I82" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="I82">
+        <v>5.2</v>
       </c>
       <c r="J82">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K82">
-        <v>0.748</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+        <v>20.8</v>
+      </c>
+      <c r="K82" t="s">
+        <v>19</v>
+      </c>
+      <c r="L82">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M82">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C83" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D83" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E83" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F83">
         <v>18693.900000000001</v>
       </c>
       <c r="G83" t="s">
+        <v>28</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
         <v>26</v>
       </c>
-      <c r="H83">
+      <c r="J83">
         <v>26</v>
       </c>
-      <c r="I83" t="s">
-        <v>27</v>
-      </c>
-      <c r="J83">
+      <c r="K83" t="s">
+        <v>29</v>
+      </c>
+      <c r="L83">
         <v>1.01</v>
       </c>
-      <c r="K83">
+      <c r="M83">
         <v>490.90199999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C84" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E84" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F84">
         <v>426</v>
       </c>
       <c r="G84" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H84">
-        <v>5.2</v>
-      </c>
-      <c r="I84" t="s">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="I84">
+        <v>5.2</v>
       </c>
       <c r="J84">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K84">
-        <v>0.19400000000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10.4</v>
+      </c>
+      <c r="K84" t="s">
+        <v>19</v>
+      </c>
+      <c r="L84">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M84">
+        <v>0.38800000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C85" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E85" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F85">
         <v>1595.4</v>
       </c>
       <c r="G85" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
         <v>26</v>
       </c>
-      <c r="I85" t="s">
-        <v>17</v>
-      </c>
       <c r="J85">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K85">
+        <v>26</v>
+      </c>
+      <c r="K85" t="s">
+        <v>19</v>
+      </c>
+      <c r="L85">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M85">
         <v>3.63</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E86" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F86">
         <v>0</v>
       </c>
       <c r="H86">
-        <v>5.2</v>
-      </c>
-      <c r="I86" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="I86">
+        <v>5.2</v>
       </c>
       <c r="J86">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K86">
+        <v>20.8</v>
+      </c>
+      <c r="K86" t="s">
+        <v>19</v>
+      </c>
+      <c r="L86">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M86">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C87" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D87" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E87" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F87">
         <v>11749.6</v>
       </c>
       <c r="G87" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H87">
-        <v>5.2</v>
-      </c>
-      <c r="I87" t="s">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="I87">
+        <v>5.2</v>
       </c>
       <c r="J87">
+        <v>20.8</v>
+      </c>
+      <c r="K87" t="s">
+        <v>29</v>
+      </c>
+      <c r="L87">
         <v>1.01</v>
       </c>
-      <c r="K87">
-        <v>61.709000000000003</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M87">
+        <v>246.83600000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F88">
         <v>0</v>
       </c>
       <c r="H88">
-        <v>5.2</v>
-      </c>
-      <c r="I88" t="s">
-        <v>17</v>
+        <v>118</v>
+      </c>
+      <c r="I88">
+        <v>5.2</v>
       </c>
       <c r="J88">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K88">
+        <v>613.6</v>
+      </c>
+      <c r="K88" t="s">
+        <v>19</v>
+      </c>
+      <c r="L88">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C89" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E89" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F89">
         <v>2534</v>
       </c>
       <c r="G89" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H89">
-        <v>5.2</v>
-      </c>
-      <c r="I89" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I89">
+        <v>5.2</v>
       </c>
       <c r="J89">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K89">
+        <v>5.2</v>
+      </c>
+      <c r="K89" t="s">
+        <v>19</v>
+      </c>
+      <c r="L89">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M89">
         <v>1.153</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B90" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C90" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E90" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F90">
         <v>5.6</v>
       </c>
       <c r="G90" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H90">
-        <v>5.2</v>
-      </c>
-      <c r="I90" t="s">
-        <v>17</v>
+        <v>53</v>
+      </c>
+      <c r="I90">
+        <v>5.2</v>
       </c>
       <c r="J90">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K90">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+        <v>275.60000000000002</v>
+      </c>
+      <c r="K90" t="s">
+        <v>19</v>
+      </c>
+      <c r="L90">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M90">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C91" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D91" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E91" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F91">
         <v>1081.9000000000001</v>
       </c>
       <c r="G91" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H91">
-        <v>5.2</v>
-      </c>
-      <c r="I91" t="s">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>5.2</v>
       </c>
       <c r="J91">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K91">
+        <v>5.2</v>
+      </c>
+      <c r="K91" t="s">
+        <v>19</v>
+      </c>
+      <c r="L91">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M91">
         <v>0.49199999999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D92" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E92" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F92">
         <v>373.8</v>
       </c>
       <c r="G92" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H92">
-        <v>5.2</v>
-      </c>
-      <c r="I92" t="s">
-        <v>17</v>
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>5.2</v>
       </c>
       <c r="J92">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K92">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15.6</v>
+      </c>
+      <c r="K92" t="s">
+        <v>19</v>
+      </c>
+      <c r="L92">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M92">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B93" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C93" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D93" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E93" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F93">
         <v>233.1</v>
       </c>
       <c r="G93" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H93">
-        <v>5.2</v>
-      </c>
-      <c r="I93" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="I93">
+        <v>5.2</v>
       </c>
       <c r="J93">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K93">
-        <v>0.106</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="K93" t="s">
+        <v>19</v>
+      </c>
+      <c r="L93">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M93">
+        <v>1.379</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B94" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C94" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E94" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F94">
         <v>202</v>
       </c>
       <c r="G94" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H94">
-        <v>5.2</v>
-      </c>
-      <c r="I94" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="I94">
+        <v>5.2</v>
       </c>
       <c r="J94">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K94">
-        <v>9.1999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+        <v>109.2</v>
+      </c>
+      <c r="K94" t="s">
+        <v>19</v>
+      </c>
+      <c r="L94">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M94">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B95" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C95" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D95" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E95" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F95">
         <v>150.6</v>
       </c>
       <c r="G95" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H95">
-        <v>5.2</v>
-      </c>
-      <c r="I95" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="I95">
+        <v>5.2</v>
       </c>
       <c r="J95">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K95">
-        <v>6.9000000000000006E-2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="K95" t="s">
+        <v>19</v>
+      </c>
+      <c r="L95">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M95">
+        <v>0.68500000000000005</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C96" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D96" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E96" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F96">
         <v>301</v>
       </c>
       <c r="G96" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H96">
-        <v>5.2</v>
-      </c>
-      <c r="I96" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="I96">
+        <v>5.2</v>
       </c>
       <c r="J96">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K96">
-        <v>0.13700000000000001</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+        <v>187.2</v>
+      </c>
+      <c r="K96" t="s">
+        <v>19</v>
+      </c>
+      <c r="L96">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M96">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B97" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C97" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D97" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E97" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F97">
         <v>149.19999999999999</v>
       </c>
       <c r="G97" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H97">
-        <v>5.2</v>
-      </c>
-      <c r="I97" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="I97">
+        <v>5.2</v>
       </c>
       <c r="J97">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K97">
-        <v>6.8000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="K97" t="s">
+        <v>19</v>
+      </c>
+      <c r="L97">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M97">
+        <v>1.3580000000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B98" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C98" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D98" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E98" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F98">
         <v>91.7</v>
       </c>
       <c r="G98" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H98">
-        <v>5.2</v>
-      </c>
-      <c r="I98" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="I98">
+        <v>5.2</v>
       </c>
       <c r="J98">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K98">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+        <v>109.2</v>
+      </c>
+      <c r="K98" t="s">
+        <v>19</v>
+      </c>
+      <c r="L98">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M98">
+        <v>0.876</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B99" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C99" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E99" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F99">
         <v>3.6</v>
       </c>
       <c r="G99" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H99">
-        <v>5.2</v>
-      </c>
-      <c r="I99" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="I99">
+        <v>5.2</v>
       </c>
       <c r="J99">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K99">
-        <v>2E-3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+        <v>166.4</v>
+      </c>
+      <c r="K99" t="s">
+        <v>19</v>
+      </c>
+      <c r="L99">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M99">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B100" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C100" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E100" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F100">
         <v>0</v>
       </c>
       <c r="H100">
-        <v>5.2</v>
-      </c>
-      <c r="I100" t="s">
-        <v>17</v>
+        <v>37</v>
+      </c>
+      <c r="I100">
+        <v>5.2</v>
       </c>
       <c r="J100">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K100">
+        <v>192.4</v>
+      </c>
+      <c r="K100" t="s">
+        <v>19</v>
+      </c>
+      <c r="L100">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M100">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C101" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D101" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E101" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F101">
         <v>202</v>
       </c>
       <c r="G101" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H101">
-        <v>5.2</v>
-      </c>
-      <c r="I101" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="I101">
+        <v>5.2</v>
       </c>
       <c r="J101">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="K101">
-        <v>9.1999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="K101" t="s">
+        <v>19</v>
+      </c>
+      <c r="L101">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="M101">
+        <v>2.298</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>295</v>
-      </c>
-      <c r="K103">
-        <v>1915.97</v>
+        <v>297</v>
+      </c>
+      <c r="M103">
+        <v>32041.98</v>
       </c>
     </row>
   </sheetData>
@@ -4997,133 +5625,139 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B4" t="s">
         <v>305</v>
       </c>
-      <c r="B4" t="s">
-        <v>303</v>
-      </c>
       <c r="C4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C6" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B7" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C10" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C11" t="s">
-        <v>321</v>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C12" t="s">
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -5133,243 +5767,249 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="45.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.5703125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C2" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B4" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B5" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C5" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B6" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C6" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C7" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B11">
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B12">
         <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B13">
         <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B14">
         <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B15">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B16" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C16" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B17" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C17" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>359</v>
-      </c>
-      <c r="B18">
-        <v>8.7499999999999994E-2</v>
+        <v>364</v>
+      </c>
+      <c r="B18" t="s">
+        <v>365</v>
       </c>
       <c r="C18" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B19">
-        <v>1.01</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="C19" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B20">
-        <v>0.55600000000000005</v>
+        <v>1.01</v>
       </c>
       <c r="C20" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>365</v>
-      </c>
-      <c r="B21" t="s">
-        <v>366</v>
+        <v>371</v>
+      </c>
+      <c r="B21">
+        <v>0.55600000000000005</v>
       </c>
       <c r="C21" t="s">
-        <v>367</v>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>373</v>
+      </c>
+      <c r="B22" t="s">
+        <v>374</v>
+      </c>
+      <c r="C22" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>
